--- a/02_DIA_inicio_2026_analisis_assets/rbd_9413_escuela-general-basica-santa-fe_nt2_rubricas.xlsx
+++ b/02_DIA_inicio_2026_analisis_assets/rbd_9413_escuela-general-basica-santa-fe_nt2_rubricas.xlsx
@@ -1992,13 +1992,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{92A213C7-3BD8-443B-AC44-5062DB2B9E7D}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{40336B43-590F-4790-9D93-32F600736B32}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A81044F4-7BF4-4F68-A5B4-2A9245938C38}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{356F0C2F-10BF-48B1-97DE-8D6F847E0EB8}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8423D98B-8D37-421F-8C18-8DB65DA301D3}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DCFD3125-C9ED-4765-8F15-ACC0420C168C}"/>
 </file>